--- a/data/trans_orig/IQ18D_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos</t>
+          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,66; 24,71</t>
+          <t>18,55; 25,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,98; 22,75</t>
+          <t>18,01; 23,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 18,54</t>
+          <t>13,98; 18,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,06; 20,13</t>
+          <t>11,99; 20,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,8; 23,48</t>
+          <t>16,76; 23,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,16; 21,33</t>
+          <t>16,27; 21,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,42; 20,13</t>
+          <t>14,44; 20,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +756,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,18; 22,81</t>
+          <t>18,26; 22,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,72; 21,41</t>
+          <t>17,66; 21,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,75; 18,38</t>
+          <t>14,65; 18,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 20,38</t>
+          <t>12,21; 19,74</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,67; 21,72</t>
+          <t>18,63; 21,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,03; 21,84</t>
+          <t>18,02; 22,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,29; 19,07</t>
+          <t>15,42; 19,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,52; 39,25</t>
+          <t>15,07; 39,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 21,72</t>
+          <t>18,5; 21,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,59; 23,58</t>
+          <t>19,46; 23,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,34; 19,05</t>
+          <t>15,15; 18,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 28,67</t>
+          <t>13,18; 27,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,98</t>
+          <t>18,97; 21,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,3; 22,22</t>
+          <t>19,31; 22,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 18,34</t>
+          <t>15,68; 18,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,03; 29,9</t>
+          <t>15,85; 29,4</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,65; 22,13</t>
+          <t>17,83; 22,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,32; 23,45</t>
+          <t>18,26; 23,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,98; 21,08</t>
+          <t>15,92; 21,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 16,76</t>
+          <t>8,57; 17,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,82; 24,85</t>
+          <t>20,0; 24,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,1; 21,58</t>
+          <t>17,18; 21,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 18,16</t>
+          <t>14,32; 18,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,09; 17,68</t>
+          <t>9,86; 17,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,52; 22,64</t>
+          <t>19,38; 22,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,32; 21,44</t>
+          <t>18,27; 21,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,66; 18,84</t>
+          <t>15,71; 18,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,96; 15,43</t>
+          <t>10,01; 15,46</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,31; 29,76</t>
+          <t>23,34; 30,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 21,94</t>
+          <t>17,97; 22,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,07; 20,16</t>
+          <t>15,14; 20,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 26,0</t>
+          <t>13,01; 25,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,46; 26,13</t>
+          <t>21,52; 26,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,79; 23,94</t>
+          <t>19,68; 23,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 25,44</t>
+          <t>16,75; 25,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,37; 39,63</t>
+          <t>12,55; 39,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,06; 26,99</t>
+          <t>23,23; 26,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 22,35</t>
+          <t>19,47; 22,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,4; 21,21</t>
+          <t>16,49; 21,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,38; 34,38</t>
+          <t>14,33; 32,93</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,59; 23,11</t>
+          <t>20,53; 23,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,05; 21,31</t>
+          <t>18,99; 21,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,98; 18,19</t>
+          <t>16,1; 18,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 21,95</t>
+          <t>14,05; 22,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,12; 22,51</t>
+          <t>20,16; 22,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,27; 21,55</t>
+          <t>19,26; 21,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,97; 18,61</t>
+          <t>16,07; 18,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 22,99</t>
+          <t>13,64; 23,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,73; 22,36</t>
+          <t>20,71; 22,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,47; 21,01</t>
+          <t>19,45; 21,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 17,97</t>
+          <t>16,26; 17,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,61</t>
+          <t>14,53; 20,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Edad-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,55; 25,02</t>
+          <t>18,57; 24,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 23,15</t>
+          <t>18,03; 23,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,98; 18,77</t>
+          <t>14,02; 19,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,99; 20,2</t>
+          <t>11,87; 20,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,76; 23,74</t>
+          <t>16,71; 23,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,27; 21,62</t>
+          <t>16,18; 21,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,44; 20,18</t>
+          <t>14,45; 19,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,82; 25,12</t>
+          <t>10,59; 23,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,26; 22,67</t>
+          <t>18,35; 22,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,66; 21,14</t>
+          <t>17,58; 21,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,65; 18,17</t>
+          <t>14,78; 18,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,21; 19,74</t>
+          <t>12,23; 20,14</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,63; 21,68</t>
+          <t>18,69; 21,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,02; 22,22</t>
+          <t>18,18; 22,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 19,68</t>
+          <t>15,4; 19,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,07; 39,95</t>
+          <t>15,99; 42,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,5; 21,62</t>
+          <t>18,37; 21,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,46; 23,85</t>
+          <t>19,63; 23,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,15; 18,89</t>
+          <t>15,14; 18,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 27,81</t>
+          <t>13,16; 28,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 21,15</t>
+          <t>18,84; 20,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,31; 22,05</t>
+          <t>19,43; 22,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,68; 18,2</t>
+          <t>15,68; 18,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 29,4</t>
+          <t>16,07; 29,26</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,83; 22,08</t>
+          <t>17,7; 22,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,58</t>
+          <t>18,39; 23,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,92; 21,03</t>
+          <t>16,11; 21,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,57; 17,14</t>
+          <t>8,74; 17,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,0; 24,8</t>
+          <t>19,96; 24,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,18; 21,56</t>
+          <t>16,98; 21,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,32; 18,12</t>
+          <t>14,42; 17,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 17,59</t>
+          <t>10,03; 18,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,38; 22,66</t>
+          <t>19,37; 22,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,27; 21,65</t>
+          <t>18,3; 21,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,71; 18,78</t>
+          <t>15,7; 18,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,46</t>
+          <t>10,01; 15,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,34; 30,18</t>
+          <t>23,23; 29,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,97; 22,06</t>
+          <t>17,87; 22,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,14; 20,0</t>
+          <t>15,14; 20,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,01; 25,98</t>
+          <t>13,34; 26,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,52; 26,23</t>
+          <t>21,89; 26,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,68; 23,65</t>
+          <t>19,7; 23,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,75; 25,72</t>
+          <t>16,68; 25,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 39,46</t>
+          <t>12,9; 40,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,23; 26,96</t>
+          <t>23,12; 26,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 22,29</t>
+          <t>19,55; 22,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,49; 21,0</t>
+          <t>16,47; 21,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,33; 32,93</t>
+          <t>14,15; 31,58</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,53; 23,06</t>
+          <t>20,58; 23,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 21,2</t>
+          <t>19,01; 21,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,1; 18,37</t>
+          <t>16,06; 18,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,05; 22,45</t>
+          <t>14,3; 22,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,16; 22,36</t>
+          <t>20,18; 22,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,26; 21,75</t>
+          <t>19,24; 21,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,07; 18,57</t>
+          <t>16,01; 18,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,64; 23,75</t>
+          <t>13,63; 22,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,71; 22,3</t>
+          <t>20,67; 22,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 21,05</t>
+          <t>19,47; 21,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,26; 17,96</t>
+          <t>16,31; 17,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,53; 20,56</t>
+          <t>14,55; 20,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Edad-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
+          <t>Tiempo medio en minutos que tuvieron que esperar desde que llegaron hasta ser atendidos/as en la última consulta médica (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,36</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16,63</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15,77</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>21,15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>20,18</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>15,73</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,47</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,35</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,36</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,63</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,89</t>
+          <t>15,68</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,17</t>
+          <t>15,72</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,57; 24,6</t>
+          <t>16,8; 23,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,03; 23,18</t>
+          <t>16,16; 21,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,02; 19,07</t>
+          <t>14,42; 20,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,87; 20,08</t>
+          <t>11,02; 28,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,71; 23,46</t>
+          <t>18,66; 24,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,18; 21,38</t>
+          <t>17,98; 22,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 19,66</t>
+          <t>14,03; 18,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 23,52</t>
+          <t>12,28; 20,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,35; 22,91</t>
+          <t>18,18; 22,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,58; 21,14</t>
+          <t>17,72; 21,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 18,26</t>
+          <t>14,75; 18,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 20,14</t>
+          <t>12,68; 21,74</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,85</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21,36</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,79</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18,48</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>20,06</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,89</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>17,01</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23,11</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,85</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,36</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,79</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,16</t>
+          <t>21,78</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,45</t>
+          <t>20,04</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,69; 21,78</t>
+          <t>18,6; 21,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 22,02</t>
+          <t>19,59; 23,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,4; 19,12</t>
+          <t>15,34; 19,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,99; 42,23</t>
+          <t>13,24; 30,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,37; 21,44</t>
+          <t>18,67; 21,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,63; 23,66</t>
+          <t>18,03; 21,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 18,81</t>
+          <t>15,29; 19,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,16; 28,59</t>
+          <t>14,55; 36,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,84; 20,95</t>
+          <t>18,77; 20,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,43; 22,24</t>
+          <t>19,3; 22,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,68; 18,35</t>
+          <t>15,72; 18,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,07; 29,26</t>
+          <t>15,66; 29,49</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21,96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,03</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,06</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12,57</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19,75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>20,58</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18,02</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,55</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,96</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,03</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,06</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,92</t>
+          <t>11,78</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,29</t>
+          <t>12,21</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,7; 22,11</t>
+          <t>19,82; 24,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,39; 23,48</t>
+          <t>17,1; 21,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,11; 21,61</t>
+          <t>14,33; 18,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 17,39</t>
+          <t>9,85; 16,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,96; 24,43</t>
+          <t>17,65; 22,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,98; 21,55</t>
+          <t>18,32; 23,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,42; 17,92</t>
+          <t>15,98; 21,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 18,35</t>
+          <t>8,71; 17,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,37; 22,63</t>
+          <t>19,52; 22,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 21,69</t>
+          <t>18,32; 21,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,7; 18,94</t>
+          <t>15,66; 18,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,64</t>
+          <t>10,01; 15,07</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23,74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,61</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,34</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20,59</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>25,81</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>19,87</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17,02</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,81</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,74</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,61</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,34</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,58</t>
+          <t>17,47</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,52</t>
+          <t>19,35</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,23; 29,56</t>
+          <t>21,46; 26,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 22,15</t>
+          <t>19,79; 23,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,14; 20,22</t>
+          <t>16,59; 25,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,34; 26,22</t>
+          <t>12,46; 39,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,89; 26,35</t>
+          <t>23,31; 29,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,7; 23,86</t>
+          <t>18,08; 21,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,68; 25,48</t>
+          <t>15,07; 20,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,9; 40,68</t>
+          <t>12,91; 24,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,12; 26,86</t>
+          <t>23,06; 26,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,55; 22,54</t>
+          <t>19,29; 22,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,47; 21,2</t>
+          <t>16,4; 21,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,15; 31,58</t>
+          <t>14,45; 34,06</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20,34</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17,07</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>21,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,1</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>17,02</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,2</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>20,34</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,11</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,97</t>
+          <t>16,59</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,98</t>
+          <t>16,86</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,58; 23,14</t>
+          <t>20,12; 22,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,01; 21,25</t>
+          <t>19,27; 21,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,06; 18,27</t>
+          <t>15,97; 18,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,3; 22,63</t>
+          <t>13,8; 23,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,18; 22,44</t>
+          <t>20,59; 23,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,24; 21,49</t>
+          <t>19,05; 21,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 18,51</t>
+          <t>15,98; 18,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 22,59</t>
+          <t>13,84; 20,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,67; 22,35</t>
+          <t>20,73; 22,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,47; 21,02</t>
+          <t>19,47; 21,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 17,96</t>
+          <t>16,32; 17,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,73</t>
+          <t>14,58; 20,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>19,35</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18,36</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16,63</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,18</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,73</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15,68</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20,21</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19,28</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16,17</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,72</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>19.35424059921437</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>18.36058277699301</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>16.62870214922603</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>15.77478740259055</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>21.15326143196667</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>20.1776506375156</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>15.73150598726913</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>15.67519524961799</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>20.20916829919453</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>19.27617784121735</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>16.16561116330465</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>15.7245239903502</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>16,8; 23,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16,16; 21,33</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14,42; 20,13</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11,02; 28,78</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,66; 24,71</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,98; 22,75</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14,03; 18,54</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12,28; 20,29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18,18; 22,81</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17,72; 21,41</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14,75; 18,38</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,68; 21,74</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>16.79556671282548</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>16.16327541773453</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>14.42451372900966</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>11.02191943271833</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>18.65885863310158</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>17.98260927908715</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>14.03457482446691</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>12.28489398498434</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>18.1773325933997</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>17.71862238534525</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>14.75459411620556</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>12.68242652389059</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>23.47991330736938</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>21.33493975946632</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>20.1290825019064</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>28.77875897082211</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>24.71105374893455</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>22.74603357176341</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>18.54021214853392</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>20.28565545214106</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>22.81026660234493</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>21.4106967484771</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>18.3779480850355</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>21.74119456596035</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>19,85</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>21,36</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16,79</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,48</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,06</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,89</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,01</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21,78</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19,95</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20,68</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16,89</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>20,04</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>18,6; 21,72</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19,59; 23,58</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15,34; 19,05</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13,24; 30,03</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18,67; 21,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,03; 21,84</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,29; 19,07</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14,55; 36,24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18,77; 20,98</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19,3; 22,22</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15,72; 18,34</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,66; 29,49</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>19.84550056534612</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>21.36481391762977</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>16.79166727898914</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>18.48277586569165</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>20.0557311425892</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>19.89411105488223</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>17.01132692065269</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>21.77835540151993</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>19.95151060116538</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>20.67808181729337</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>16.89280549027111</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>20.0434844498493</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>21,96</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19,03</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16,06</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,75</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,58</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,02</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11,78</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20,9</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>19,8</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>17,03</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,21</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>18.59671516763678</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>19.59471711554088</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>15.33535287874518</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>13.23950083641843</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>18.67000029114171</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>18.02733926875747</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>15.28777654058825</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>14.5543258251199</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>18.76862352394504</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>19.30013407512124</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>15.72117295698826</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>15.65772004481373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>19,82; 24,85</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>17,1; 21,58</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>14,33; 18,16</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,85; 16,26</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>17,65; 22,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>18,32; 23,45</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,98; 21,08</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8,71; 17,35</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19,52; 22,64</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>18,32; 21,44</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>15,66; 18,84</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>10,01; 15,07</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>21.7190138175718</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>23.57667933995994</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>19.04897635379815</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>30.03146258647896</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>21.72029955219325</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>21.83604160108185</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>19.07244252429732</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>36.23621720507388</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>20.97582520860058</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>22.21655890597406</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>18.3416137546883</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>29.48964710299837</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>23,74</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21,61</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,34</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20,59</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,81</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,87</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,02</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17,47</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>24,72</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20,77</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18,14</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,35</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>21.96258239752681</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>19.02805850847443</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>16.05705647521604</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>12.57179104632348</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>19.75010238058384</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>20.58158495286409</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>18.01501877969402</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>11.77838854665341</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>20.89524057140092</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>19.80460552780933</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>17.02532582126138</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>12.21045871674628</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>21,46; 26,13</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>19,79; 23,94</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16,59; 25,44</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12,46; 39,33</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23,31; 29,76</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,08; 21,94</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,07; 20,16</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12,91; 24,96</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23,06; 26,99</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19,29; 22,35</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>16,4; 21,21</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 34,06</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>19.8214856417406</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>17.10269036605301</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>14.32900351748965</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>9.845914587405145</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>17.6533003992876</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>18.32204676037238</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>15.97595717216127</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>8.707711389793646</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>19.52022099871418</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>18.3179744256417</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>15.6573305363456</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>10.01108900972183</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>24.84502733505361</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>21.58066267665136</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18.15609810826334</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>16.26444684020251</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>22.13334450817497</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>23.44928637944947</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>21.08497633440517</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>17.35341488515261</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>22.6449594971649</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>21.43946716738943</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>18.83588562425114</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>15.07291354089681</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>23.74476785439763</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>21.60750708930899</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>19.34313474001858</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>20.58870573100066</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>25.80528677155203</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>19.87488424269791</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>17.01893297735725</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>17.46924266869386</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>24.72443902435623</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>20.76539288685225</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>18.13887062855549</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>19.35299008460329</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>21.45690999139775</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>19.78548620717096</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>16.59336540840775</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>12.45830724492561</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>23.31264343943491</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>18.07584447101746</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>15.06521239119247</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>12.91414717679039</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>23.06369349769973</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>19.28818412453176</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>16.40413977749267</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>14.44540504388588</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>26.12815202324574</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>23.93747055052402</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>25.44411101411246</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>39.32782860329647</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>29.76031106240329</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>21.93877905083399</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>20.1582736163884</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>24.96277731459789</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>26.99036290708664</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>22.3455700654226</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>21.20956016505447</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>34.05521248998152</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>21,2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>20,34</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,07</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,68</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>20,1</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,02</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16,59</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21,44</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>20,22</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17,07</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>16,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>20,12; 22,51</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19,27; 21,55</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15,97; 18,61</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13,8; 23,49</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>20,59; 23,11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,05; 21,31</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,98; 18,19</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13,84; 20,95</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20,73; 22,36</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19,47; 21,01</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16,32; 17,97</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,58; 20,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>21.20315367394295</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>20.34115060108572</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>17.10992561735796</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>17.07415936286198</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>21.68045002578471</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>20.10049855844353</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>17.02227172167003</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>16.58984697811489</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>21.43586351863019</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>20.22420121244805</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>17.06674495947114</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>16.856725395439</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>20.12439648941209</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>19.27295014365711</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>15.96789560650419</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>13.80329169288218</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>20.58500862176672</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>19.05194290084968</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>15.97721124196729</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>13.84105478791669</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>20.73365726329215</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>19.47063881498873</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>16.31656524892515</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>14.58252901200152</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>22.51042969387167</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>21.54544377606527</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>18.61264151134981</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>23.49436494382347</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>23.11160996594476</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>21.31238342408531</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>18.18597390600504</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>20.95348885620419</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>22.36101052858173</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>21.01251229446648</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>17.9723657073723</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>20.2898407291083</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
